--- a/main_processing/summary_results/results_stats.xlsx
+++ b/main_processing/summary_results/results_stats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Backup\Desktop\Grad\3rd_Year\EIC_Manuscript\spatialaveraging_testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Documents\GitHub\EIC_manuscript\main_processing\summary_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AFD5D6-01CF-4440-B916-EB671767138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C41A7B-9B95-41F3-B404-7BF3F2729195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4452" yWindow="1512" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReSALT_values" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="TimeSeries" sheetId="4" r:id="rId4"/>
     <sheet name="TL_Age" sheetId="5" r:id="rId5"/>
     <sheet name="Mean r2" sheetId="6" r:id="rId6"/>
+    <sheet name="ADDT" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="111">
   <si>
     <t>Year</t>
   </si>
@@ -365,6 +366,15 @@
   </si>
   <si>
     <t>Thaw Season Length</t>
+  </si>
+  <si>
+    <t>Median_Subsidence</t>
+  </si>
+  <si>
+    <t>Median_EIC_percent</t>
+  </si>
+  <si>
+    <t>Precip</t>
   </si>
 </sst>
 </file>
@@ -8690,4 +8700,137 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA21557-DC7E-4A6F-8F8A-F10950C41832}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C2" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="D2">
+        <v>310</v>
+      </c>
+      <c r="E2">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D3">
+        <v>613</v>
+      </c>
+      <c r="E3">
+        <v>25.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="D4">
+        <v>305</v>
+      </c>
+      <c r="E4">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="D5">
+        <v>278</v>
+      </c>
+      <c r="E5">
+        <v>19.88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="C6" s="6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D6">
+        <v>326</v>
+      </c>
+      <c r="E6">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="C7" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="D7">
+        <v>517</v>
+      </c>
+      <c r="E7">
+        <v>22.17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main_processing/summary_results/results_stats.xlsx
+++ b/main_processing/summary_results/results_stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Documents\GitHub\EIC_manuscript\main_processing\summary_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C41A7B-9B95-41F3-B404-7BF3F2729195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2639911-16FB-4EB1-9008-B32448ECD9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4452" yWindow="1512" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReSALT_values" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="116">
   <si>
     <t>Year</t>
   </si>
@@ -375,12 +375,30 @@
   </si>
   <si>
     <t>Precip</t>
+  </si>
+  <si>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>Inland Average</t>
+  </si>
+  <si>
+    <t>Coastal Average</t>
+  </si>
+  <si>
+    <t>Mean_E_Uncert_2019</t>
+  </si>
+  <si>
+    <t>Mean_E_Uncert_2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -522,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -569,6 +587,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6899,15 +6919,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>231493</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>99349</xdr:rowOff>
+      <xdr:colOff>244364</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>147026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1307756</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>20595</xdr:rowOff>
+      <xdr:colOff>1324437</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>68271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8250,7 +8270,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9F15C4-2ABE-401A-A7E7-6DA16866D145}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -8259,9 +8279,11 @@
     <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.77734375" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>79</v>
       </c>
@@ -8295,8 +8317,14 @@
       <c r="K1" s="17" t="s">
         <v>102</v>
       </c>
+      <c r="L1" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -8330,8 +8358,14 @@
       <c r="K2">
         <v>0.3</v>
       </c>
+      <c r="L2" s="25">
+        <v>0.63431999999999999</v>
+      </c>
+      <c r="M2" s="25">
+        <v>0.33010299999999998</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -8365,8 +8399,14 @@
       <c r="K3">
         <v>0.9</v>
       </c>
+      <c r="L3" s="25">
+        <v>0.97899599999999998</v>
+      </c>
+      <c r="M3" s="25">
+        <v>0.57900200000000002</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -8400,8 +8440,14 @@
       <c r="K4">
         <v>3</v>
       </c>
+      <c r="L4" s="25">
+        <v>0.79219600000000001</v>
+      </c>
+      <c r="M4" s="25">
+        <v>0.63818799999999998</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -8435,8 +8481,14 @@
       <c r="K5">
         <v>1</v>
       </c>
+      <c r="L5" s="25">
+        <v>0.81395200000000001</v>
+      </c>
+      <c r="M5" s="25">
+        <v>0.46308199999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -8470,8 +8522,14 @@
       <c r="K6">
         <v>1.2</v>
       </c>
+      <c r="L6" s="25">
+        <v>0.80269999999999997</v>
+      </c>
+      <c r="M6" s="25">
+        <v>0.524648</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -8505,8 +8563,14 @@
       <c r="K7">
         <v>2.9</v>
       </c>
+      <c r="L7" s="25">
+        <v>0.84271799999999997</v>
+      </c>
+      <c r="M7" s="25">
+        <v>0.34269300000000003</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -8540,8 +8604,14 @@
       <c r="K8">
         <v>1.6</v>
       </c>
+      <c r="L8" s="25">
+        <v>0.63564299999999996</v>
+      </c>
+      <c r="M8" s="25">
+        <v>0.33698600000000001</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -8574,6 +8644,51 @@
       </c>
       <c r="K9">
         <v>2.1</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0.46011800000000003</v>
+      </c>
+      <c r="M9" s="25">
+        <v>0.26873200000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11">
+        <f>AVERAGE(J2:J9)</f>
+        <v>6.05</v>
+      </c>
+      <c r="K11">
+        <f>AVERAGE(K2:K9)</f>
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12">
+        <f>AVERAGE(J4,J7,J9)</f>
+        <v>6.7</v>
+      </c>
+      <c r="K12">
+        <f>AVERAGE(K4,K7,K9)</f>
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13">
+        <f>AVERAGE(J2,J3,J5,J6,J8)</f>
+        <v>5.6599999999999993</v>
+      </c>
+      <c r="K13">
+        <f>AVERAGE(K2,K3,K5,K6,K8)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/main_processing/summary_results/results_stats.xlsx
+++ b/main_processing/summary_results/results_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Documents\GitHub\EIC_manuscript\main_processing\summary_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2639911-16FB-4EB1-9008-B32448ECD9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BA33B2-5513-4D6B-8F2F-3F3C04612B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReSALT_values" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Spat_avg" sheetId="3" r:id="rId3"/>
     <sheet name="TimeSeries" sheetId="4" r:id="rId4"/>
     <sheet name="TL_Age" sheetId="5" r:id="rId5"/>
-    <sheet name="Mean r2" sheetId="6" r:id="rId6"/>
-    <sheet name="ADDT" sheetId="7" r:id="rId7"/>
+    <sheet name="TL_Age_EIC" sheetId="10" r:id="rId6"/>
+    <sheet name="Mean r2" sheetId="6" r:id="rId7"/>
+    <sheet name="ADDT" sheetId="7" r:id="rId8"/>
+    <sheet name="geomorphE19" sheetId="9" r:id="rId9"/>
+    <sheet name="geomorphEIC19" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="153">
   <si>
     <t>Year</t>
   </si>
@@ -390,6 +393,117 @@
   </si>
   <si>
     <t>Mean_E_Uncert_2021</t>
+  </si>
+  <si>
+    <t>Coalescent low-center polygons</t>
+  </si>
+  <si>
+    <t>Low-center polygons</t>
+  </si>
+  <si>
+    <t>Nonpatterned Drained Thaw Lake Basins </t>
+  </si>
+  <si>
+    <t>Drained slope</t>
+  </si>
+  <si>
+    <t>Flat-center polygons</t>
+  </si>
+  <si>
+    <t>High-center polygons </t>
+  </si>
+  <si>
+    <t>Sandy barrens</t>
+  </si>
+  <si>
+    <t>Sand dunes</t>
+  </si>
+  <si>
+    <t>Coastal saline waters</t>
+  </si>
+  <si>
+    <t>Rivers</t>
+  </si>
+  <si>
+    <t>Urban (i.e. towns and roads)</t>
+  </si>
+  <si>
+    <t>Riparian corridors</t>
+  </si>
+  <si>
+    <t>Ponds</t>
+  </si>
+  <si>
+    <t>Small lakes</t>
+  </si>
+  <si>
+    <t>Medium lakes</t>
+  </si>
+  <si>
+    <t>Large lakes</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>class_name</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>OBJECTID *</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>RANGE</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>PCT90</t>
+  </si>
+  <si>
+    <t>PercentTOTAL</t>
+  </si>
+  <si>
+    <t>Med_EIC_2019</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
+  <si>
+    <t>Inland Avg</t>
+  </si>
+  <si>
+    <t>Coastal Avg</t>
+  </si>
+  <si>
+    <t>Med_EIC_2021</t>
+  </si>
+  <si>
+    <t>Med_EIC_Uncert_2019</t>
+  </si>
+  <si>
+    <t>Med_EIC_Uncert_2021</t>
   </si>
 </sst>
 </file>
@@ -397,7 +511,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -575,6 +689,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -588,7 +703,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7352,26 +7466,26 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20"/>
+      <c r="C1" s="21"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20" t="s">
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20" t="s">
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -7666,6 +7780,736 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF7E68A-EDBB-4BD3-AF33-8C03844816FE}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2">
+        <v>724</v>
+      </c>
+      <c r="D2">
+        <v>3.68E-4</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>145.486603</v>
+      </c>
+      <c r="G2">
+        <v>145.486603</v>
+      </c>
+      <c r="H2">
+        <v>37.547438999999997</v>
+      </c>
+      <c r="I2">
+        <v>26.649277000000001</v>
+      </c>
+      <c r="J2">
+        <v>27184.345795000001</v>
+      </c>
+      <c r="K2">
+        <v>32.870865000000002</v>
+      </c>
+      <c r="L2">
+        <v>75.669032000000001</v>
+      </c>
+      <c r="M2">
+        <f>$C2/(SUM($C$2:$C$17))*100</f>
+        <v>0.54971754844196075</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>88.457565000000002</v>
+      </c>
+      <c r="G3">
+        <v>88.457565000000002</v>
+      </c>
+      <c r="H3">
+        <v>24.579640999999999</v>
+      </c>
+      <c r="I3">
+        <v>14.510312000000001</v>
+      </c>
+      <c r="J3">
+        <v>3391.9904940000001</v>
+      </c>
+      <c r="K3">
+        <v>23.63035</v>
+      </c>
+      <c r="L3">
+        <v>35.801223</v>
+      </c>
+      <c r="M3">
+        <f>$C3/(SUM($C$2:$C$17))*100</f>
+        <v>0.10478041669197595</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4">
+        <v>974</v>
+      </c>
+      <c r="D4">
+        <v>4.9600000000000002E-4</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>103.512253</v>
+      </c>
+      <c r="G4">
+        <v>103.512253</v>
+      </c>
+      <c r="H4">
+        <v>23.341099</v>
+      </c>
+      <c r="I4">
+        <v>15.476107000000001</v>
+      </c>
+      <c r="J4">
+        <v>22734.230373999999</v>
+      </c>
+      <c r="K4">
+        <v>21.14678</v>
+      </c>
+      <c r="L4">
+        <v>41.026603000000001</v>
+      </c>
+      <c r="M4">
+        <f>$C4/(SUM($C$2:$C$17))*100</f>
+        <v>0.73953714389843894</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="E5">
+        <v>6.3654140000000003</v>
+      </c>
+      <c r="F5">
+        <v>38.509734999999999</v>
+      </c>
+      <c r="G5">
+        <v>32.144320999999998</v>
+      </c>
+      <c r="H5">
+        <v>18.922315000000001</v>
+      </c>
+      <c r="I5">
+        <v>9.6517079999999993</v>
+      </c>
+      <c r="J5">
+        <v>189.22315</v>
+      </c>
+      <c r="K5">
+        <v>20.565424</v>
+      </c>
+      <c r="L5">
+        <v>26.036200999999998</v>
+      </c>
+      <c r="M5">
+        <f>$C5/(SUM($C$2:$C$17))*100</f>
+        <v>7.5927838182591268E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6">
+        <v>801</v>
+      </c>
+      <c r="D6">
+        <v>4.0700000000000003E-4</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>87.374046000000007</v>
+      </c>
+      <c r="G6">
+        <v>87.374046000000007</v>
+      </c>
+      <c r="H6">
+        <v>18.334453</v>
+      </c>
+      <c r="I6">
+        <v>11.810112999999999</v>
+      </c>
+      <c r="J6">
+        <v>14685.896805</v>
+      </c>
+      <c r="K6">
+        <v>17.674709</v>
+      </c>
+      <c r="L6">
+        <v>34.941875000000003</v>
+      </c>
+      <c r="M6">
+        <f>$C6/(SUM($C$2:$C$17))*100</f>
+        <v>0.60818198384255606</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7">
+        <v>17147</v>
+      </c>
+      <c r="D7">
+        <v>8.7229999999999999E-3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>121.958755</v>
+      </c>
+      <c r="G7">
+        <v>121.958755</v>
+      </c>
+      <c r="H7">
+        <v>17.94088</v>
+      </c>
+      <c r="I7">
+        <v>11.33649</v>
+      </c>
+      <c r="J7">
+        <v>307632.27674</v>
+      </c>
+      <c r="K7">
+        <v>15.326461</v>
+      </c>
+      <c r="L7">
+        <v>33.462648999999999</v>
+      </c>
+      <c r="M7">
+        <f>$C7/(SUM($C$2:$C$17))*100</f>
+        <v>13.019346413168925</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8">
+        <v>410</v>
+      </c>
+      <c r="D8">
+        <v>2.0900000000000001E-4</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>89.319748000000004</v>
+      </c>
+      <c r="G8">
+        <v>89.319748000000004</v>
+      </c>
+      <c r="H8">
+        <v>21.427067999999998</v>
+      </c>
+      <c r="I8">
+        <v>18.240487000000002</v>
+      </c>
+      <c r="J8">
+        <v>8785.0979659999994</v>
+      </c>
+      <c r="K8">
+        <v>13.911077000000001</v>
+      </c>
+      <c r="L8">
+        <v>48.830938000000003</v>
+      </c>
+      <c r="M8">
+        <f>$C8/(SUM($C$2:$C$17))*100</f>
+        <v>0.31130413654862421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9">
+        <v>4753</v>
+      </c>
+      <c r="D9">
+        <v>2.418E-3</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>61.280589999999997</v>
+      </c>
+      <c r="G9">
+        <v>61.280589999999997</v>
+      </c>
+      <c r="H9">
+        <v>14.590149</v>
+      </c>
+      <c r="I9">
+        <v>8.0337759999999996</v>
+      </c>
+      <c r="J9">
+        <v>69346.978531000001</v>
+      </c>
+      <c r="K9">
+        <v>13.353236000000001</v>
+      </c>
+      <c r="L9">
+        <v>25.210070999999999</v>
+      </c>
+      <c r="M9">
+        <f>$C9/(SUM($C$2:$C$17))*100</f>
+        <v>3.6088501488185627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10">
+        <v>35795</v>
+      </c>
+      <c r="D10">
+        <v>1.821E-2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>113.326904</v>
+      </c>
+      <c r="G10">
+        <v>113.326904</v>
+      </c>
+      <c r="H10">
+        <v>15.187573</v>
+      </c>
+      <c r="I10">
+        <v>9.9518780000000007</v>
+      </c>
+      <c r="J10">
+        <v>543639.16912099998</v>
+      </c>
+      <c r="K10">
+        <v>12.502442</v>
+      </c>
+      <c r="L10">
+        <v>27.927783999999999</v>
+      </c>
+      <c r="M10">
+        <f>$C10/(SUM($C$2:$C$17))*100</f>
+        <v>27.178369677458541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11">
+        <v>2312</v>
+      </c>
+      <c r="D11">
+        <v>1.176E-3</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>70.972594999999998</v>
+      </c>
+      <c r="G11">
+        <v>70.972594999999998</v>
+      </c>
+      <c r="H11">
+        <v>15.743499</v>
+      </c>
+      <c r="I11">
+        <v>10.676482999999999</v>
+      </c>
+      <c r="J11">
+        <v>36398.970341</v>
+      </c>
+      <c r="K11">
+        <v>12.356892999999999</v>
+      </c>
+      <c r="L11">
+        <v>30.818484999999999</v>
+      </c>
+      <c r="M11">
+        <f>$C11/(SUM($C$2:$C$17))*100</f>
+        <v>1.7554516187815099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12">
+        <v>4303</v>
+      </c>
+      <c r="D12">
+        <v>2.189E-3</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>82.563231999999999</v>
+      </c>
+      <c r="G12">
+        <v>82.563231999999999</v>
+      </c>
+      <c r="H12">
+        <v>14.409238999999999</v>
+      </c>
+      <c r="I12">
+        <v>10.08023</v>
+      </c>
+      <c r="J12">
+        <v>62002.954939000003</v>
+      </c>
+      <c r="K12">
+        <v>11.474724</v>
+      </c>
+      <c r="L12">
+        <v>27.432120999999999</v>
+      </c>
+      <c r="M12">
+        <f>$C12/(SUM($C$2:$C$17))*100</f>
+        <v>3.267174876996902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13">
+        <v>561</v>
+      </c>
+      <c r="D13">
+        <v>2.8499999999999999E-4</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>51.124428000000002</v>
+      </c>
+      <c r="G13">
+        <v>51.124428000000002</v>
+      </c>
+      <c r="H13">
+        <v>13.869515</v>
+      </c>
+      <c r="I13">
+        <v>8.7993210000000008</v>
+      </c>
+      <c r="J13">
+        <v>7780.7981609999997</v>
+      </c>
+      <c r="K13">
+        <v>11.241649000000001</v>
+      </c>
+      <c r="L13">
+        <v>26.266939000000001</v>
+      </c>
+      <c r="M13">
+        <f>$C13/(SUM($C$2:$C$17))*100</f>
+        <v>0.42595517220433698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14">
+        <v>2937</v>
+      </c>
+      <c r="D14">
+        <v>1.4940000000000001E-3</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>69.931213</v>
+      </c>
+      <c r="G14">
+        <v>69.931213</v>
+      </c>
+      <c r="H14">
+        <v>13.208572</v>
+      </c>
+      <c r="I14">
+        <v>8.8069919999999993</v>
+      </c>
+      <c r="J14">
+        <v>38793.576687000001</v>
+      </c>
+      <c r="K14">
+        <v>10.860072000000001</v>
+      </c>
+      <c r="L14">
+        <v>24.258673000000002</v>
+      </c>
+      <c r="M14">
+        <f>$C14/(SUM($C$2:$C$17))*100</f>
+        <v>2.2300006074227054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15">
+        <v>7212</v>
+      </c>
+      <c r="D15">
+        <v>3.669E-3</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>62.101322000000003</v>
+      </c>
+      <c r="G15">
+        <v>62.101322000000003</v>
+      </c>
+      <c r="H15">
+        <v>12.938681000000001</v>
+      </c>
+      <c r="I15">
+        <v>8.0361879999999992</v>
+      </c>
+      <c r="J15">
+        <v>93313.770640000002</v>
+      </c>
+      <c r="K15">
+        <v>10.852884</v>
+      </c>
+      <c r="L15">
+        <v>23.926466000000001</v>
+      </c>
+      <c r="M15">
+        <f>$C15/(SUM($C$2:$C$17))*100</f>
+        <v>5.475915689728482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>15199</v>
+      </c>
+      <c r="D16">
+        <v>7.7320000000000002E-3</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>114.813957</v>
+      </c>
+      <c r="G16">
+        <v>114.813957</v>
+      </c>
+      <c r="H16">
+        <v>11.751287</v>
+      </c>
+      <c r="I16">
+        <v>7.6481180000000002</v>
+      </c>
+      <c r="J16">
+        <v>178607.81723799999</v>
+      </c>
+      <c r="K16">
+        <v>9.9698150000000005</v>
+      </c>
+      <c r="L16">
+        <v>19.928699000000002</v>
+      </c>
+      <c r="M16">
+        <f>$C16/(SUM($C$2:$C$17))*100</f>
+        <v>11.540272125372047</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17">
+        <v>38428</v>
+      </c>
+      <c r="D17">
+        <v>1.9550000000000001E-2</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>95.515945000000002</v>
+      </c>
+      <c r="G17">
+        <v>95.515945000000002</v>
+      </c>
+      <c r="H17">
+        <v>10.840688</v>
+      </c>
+      <c r="I17">
+        <v>7.2389859999999997</v>
+      </c>
+      <c r="J17">
+        <v>416585.96245300001</v>
+      </c>
+      <c r="K17">
+        <v>9.0743290000000005</v>
+      </c>
+      <c r="L17">
+        <v>18.99119</v>
+      </c>
+      <c r="M17">
+        <f>$C17/(SUM($C$2:$C$17))*100</f>
+        <v>29.177549656806175</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M17">
+    <sortCondition descending="1" ref="K1:K17"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7919,15 +8763,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -8045,15 +8889,15 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -8146,10 +8990,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23"/>
+      <c r="C1" s="24"/>
       <c r="D1" t="s">
         <v>103</v>
       </c>
@@ -8317,10 +9161,10 @@
       <c r="K1" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="3" t="s">
         <v>115</v>
       </c>
     </row>
@@ -8358,10 +9202,10 @@
       <c r="K2">
         <v>0.3</v>
       </c>
-      <c r="L2" s="25">
+      <c r="L2" s="20">
         <v>0.63431999999999999</v>
       </c>
-      <c r="M2" s="25">
+      <c r="M2" s="20">
         <v>0.33010299999999998</v>
       </c>
     </row>
@@ -8399,10 +9243,10 @@
       <c r="K3">
         <v>0.9</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="20">
         <v>0.97899599999999998</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="20">
         <v>0.57900200000000002</v>
       </c>
     </row>
@@ -8440,10 +9284,10 @@
       <c r="K4">
         <v>3</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="20">
         <v>0.79219600000000001</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="20">
         <v>0.63818799999999998</v>
       </c>
     </row>
@@ -8481,10 +9325,10 @@
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="20">
         <v>0.81395200000000001</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="20">
         <v>0.46308199999999999</v>
       </c>
     </row>
@@ -8522,10 +9366,10 @@
       <c r="K6">
         <v>1.2</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="20">
         <v>0.80269999999999997</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="20">
         <v>0.524648</v>
       </c>
     </row>
@@ -8563,10 +9407,10 @@
       <c r="K7">
         <v>2.9</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="20">
         <v>0.84271799999999997</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="20">
         <v>0.34269300000000003</v>
       </c>
     </row>
@@ -8604,10 +9448,10 @@
       <c r="K8">
         <v>1.6</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="20">
         <v>0.63564299999999996</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="20">
         <v>0.33698600000000001</v>
       </c>
     </row>
@@ -8645,10 +9489,10 @@
       <c r="K9">
         <v>2.1</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="20">
         <v>0.46011800000000003</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="20">
         <v>0.26873200000000003</v>
       </c>
     </row>
@@ -8664,6 +9508,14 @@
         <f>AVERAGE(K2:K9)</f>
         <v>1.625</v>
       </c>
+      <c r="L11" s="20">
+        <f>AVERAGE(L2:L9)</f>
+        <v>0.74508037499999991</v>
+      </c>
+      <c r="M11" s="20">
+        <f>AVERAGE(M2:M9)</f>
+        <v>0.43542924999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -8677,6 +9529,14 @@
         <f>AVERAGE(K4,K7,K9)</f>
         <v>2.6666666666666665</v>
       </c>
+      <c r="L12">
+        <f>AVERAGE(L4,L7,L9)</f>
+        <v>0.69834399999999996</v>
+      </c>
+      <c r="M12">
+        <f>AVERAGE(M4,M7,M9)</f>
+        <v>0.41653766666666669</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8689,6 +9549,14 @@
       <c r="K13">
         <f>AVERAGE(K2,K3,K5,K6,K8)</f>
         <v>1</v>
+      </c>
+      <c r="L13">
+        <f>AVERAGE(L2,L3,L5,L6,L8)</f>
+        <v>0.77312219999999987</v>
+      </c>
+      <c r="M13">
+        <f>AVERAGE(M2,M3,M5,M6,M8)</f>
+        <v>0.44676419999999994</v>
       </c>
     </row>
   </sheetData>
@@ -8702,6 +9570,454 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB75B4DC-2B7A-44C2-93AB-1567121CF63C}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" customWidth="1"/>
+    <col min="12" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2">
+        <v>70.878769000000005</v>
+      </c>
+      <c r="F2">
+        <v>-153.906792</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>17.3</v>
+      </c>
+      <c r="M2">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3">
+        <v>70.881637999999995</v>
+      </c>
+      <c r="F3">
+        <v>-153.85055299999999</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3">
+        <v>235</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3">
+        <v>9.5</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M3">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4">
+        <v>70.754256999999996</v>
+      </c>
+      <c r="F4">
+        <v>-153.748977</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4">
+        <v>285</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="K4">
+        <v>5.7</v>
+      </c>
+      <c r="L4">
+        <v>12.1</v>
+      </c>
+      <c r="M4">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5">
+        <v>70.883964000000006</v>
+      </c>
+      <c r="F5">
+        <v>-153.727487</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>305</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>35.5</v>
+      </c>
+      <c r="K5">
+        <v>1.7</v>
+      </c>
+      <c r="L5">
+        <v>26.4</v>
+      </c>
+      <c r="M5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6">
+        <v>70.882463999999999</v>
+      </c>
+      <c r="F6">
+        <v>-153.446583</v>
+      </c>
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6">
+        <v>705</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>36.1</v>
+      </c>
+      <c r="K6">
+        <v>2.4</v>
+      </c>
+      <c r="L6">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7">
+        <v>70.748589999999993</v>
+      </c>
+      <c r="F7">
+        <v>-153.952</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7">
+        <v>850</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>12.4</v>
+      </c>
+      <c r="K7">
+        <v>1.9</v>
+      </c>
+      <c r="L7">
+        <v>9.4</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8">
+        <v>70.881642999999997</v>
+      </c>
+      <c r="F8">
+        <v>-153.81123299999999</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8">
+        <v>1470</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>19.7</v>
+      </c>
+      <c r="K8">
+        <v>1.9</v>
+      </c>
+      <c r="L8">
+        <v>14.8</v>
+      </c>
+      <c r="M8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9">
+        <v>70.746572</v>
+      </c>
+      <c r="F9">
+        <v>-153.919557</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9">
+        <v>2270</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>10.1</v>
+      </c>
+      <c r="K9">
+        <v>1.7</v>
+      </c>
+      <c r="L9">
+        <v>7.8</v>
+      </c>
+      <c r="M9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>147</v>
+      </c>
+      <c r="J11">
+        <f>AVERAGE(J2:J9)</f>
+        <v>19.849999999999998</v>
+      </c>
+      <c r="K11">
+        <f>AVERAGE(K2:K9)</f>
+        <v>1.9125000000000001</v>
+      </c>
+      <c r="L11">
+        <f>AVERAGE(L2:L9)</f>
+        <v>15.074999999999999</v>
+      </c>
+      <c r="M11">
+        <f>AVERAGE(M2:M9)</f>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>148</v>
+      </c>
+      <c r="J12">
+        <f>AVERAGE(J4,J7,J9)</f>
+        <v>13.133333333333333</v>
+      </c>
+      <c r="K12">
+        <f>AVERAGE(K4,K7,K9)</f>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="L12">
+        <f>AVERAGE(L4,L7,L9)</f>
+        <v>9.7666666666666675</v>
+      </c>
+      <c r="M12">
+        <f>AVERAGE(M4,M7,M9)</f>
+        <v>4.0333333333333341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13">
+        <f>AVERAGE(J2,J3,J5,J6,J8)</f>
+        <v>23.880000000000003</v>
+      </c>
+      <c r="K13">
+        <f>AVERAGE(K2,K3,K5,K6,K8)</f>
+        <v>1.2</v>
+      </c>
+      <c r="L13">
+        <f>AVERAGE(L2,L3,L5,L6,L8)</f>
+        <v>18.259999999999998</v>
+      </c>
+      <c r="M13">
+        <f>AVERAGE(M2,M3,M5,M6,M8)</f>
+        <v>4.4599999999999991</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{377D1681-D2CD-4561-BD67-58B5F6A4E1BF}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8817,7 +10133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA21557-DC7E-4A6F-8F8A-F10950C41832}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8948,4 +10264,786 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D42146-3B3D-4C27-9426-7D7671AFC753}">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2">
+        <v>4607</v>
+      </c>
+      <c r="D2">
+        <v>2.3440000000000002E-3</v>
+      </c>
+      <c r="E2">
+        <v>4.5830999999999997E-2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>16.660489999999999</v>
+      </c>
+      <c r="H2">
+        <v>16.614659</v>
+      </c>
+      <c r="I2" s="20">
+        <v>5.290305</v>
+      </c>
+      <c r="J2">
+        <v>2.3120959999999999</v>
+      </c>
+      <c r="K2">
+        <v>24372.434228999999</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4.6848109999999998</v>
+      </c>
+      <c r="M2">
+        <v>8.5788930000000008</v>
+      </c>
+      <c r="N2">
+        <f>$C2/(SUM($C$2:$C$17))*100</f>
+        <v>3.0724803926799336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>38397</v>
+      </c>
+      <c r="D3">
+        <v>1.9533999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>6.2798999999999994E-2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>19.544087999999999</v>
+      </c>
+      <c r="H3">
+        <v>19.481289</v>
+      </c>
+      <c r="I3" s="20">
+        <v>5.7574149999999999</v>
+      </c>
+      <c r="J3">
+        <v>2.398174</v>
+      </c>
+      <c r="K3">
+        <v>221067.47383599999</v>
+      </c>
+      <c r="L3" s="20">
+        <v>5.1605259999999999</v>
+      </c>
+      <c r="M3">
+        <v>9.1302830000000004</v>
+      </c>
+      <c r="N3">
+        <f>$C3/(SUM($C$2:$C$17))*100</f>
+        <v>25.607560155791496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4">
+        <v>19077</v>
+      </c>
+      <c r="D4">
+        <v>9.7050000000000001E-3</v>
+      </c>
+      <c r="E4">
+        <v>6.8499999999999995E-4</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>22.62067</v>
+      </c>
+      <c r="H4">
+        <v>22.619985</v>
+      </c>
+      <c r="I4" s="20">
+        <v>6.1604219999999996</v>
+      </c>
+      <c r="J4">
+        <v>2.885014</v>
+      </c>
+      <c r="K4">
+        <v>117522.365229</v>
+      </c>
+      <c r="L4" s="20">
+        <v>5.5759090000000002</v>
+      </c>
+      <c r="M4">
+        <v>10.313598000000001</v>
+      </c>
+      <c r="N4">
+        <f>$C4/(SUM($C$2:$C$17))*100</f>
+        <v>12.72274982660193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5">
+        <v>16321</v>
+      </c>
+      <c r="D5">
+        <v>8.3029999999999996E-3</v>
+      </c>
+      <c r="E5">
+        <v>4.5310000000000003E-2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>17.568557999999999</v>
+      </c>
+      <c r="H5">
+        <v>17.523247000000001</v>
+      </c>
+      <c r="I5" s="20">
+        <v>6.3288960000000003</v>
+      </c>
+      <c r="J5">
+        <v>2.171116</v>
+      </c>
+      <c r="K5">
+        <v>103293.90561099999</v>
+      </c>
+      <c r="L5" s="20">
+        <v>5.9660849999999996</v>
+      </c>
+      <c r="M5">
+        <v>9.3300599999999996</v>
+      </c>
+      <c r="N5">
+        <f>$C5/(SUM($C$2:$C$17))*100</f>
+        <v>10.884730299311743</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>7991</v>
+      </c>
+      <c r="D6">
+        <v>4.065E-3</v>
+      </c>
+      <c r="E6">
+        <v>0.25051800000000002</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>18.078802</v>
+      </c>
+      <c r="H6">
+        <v>17.828284</v>
+      </c>
+      <c r="I6" s="20">
+        <v>5.4433720000000001</v>
+      </c>
+      <c r="J6">
+        <v>2.045506</v>
+      </c>
+      <c r="K6">
+        <v>43497.985368000001</v>
+      </c>
+      <c r="L6" s="20">
+        <v>4.9719379999999997</v>
+      </c>
+      <c r="M6">
+        <v>8.1958540000000006</v>
+      </c>
+      <c r="N6">
+        <f>$C6/(SUM($C$2:$C$17))*100</f>
+        <v>5.3293229472336341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7">
+        <v>42606</v>
+      </c>
+      <c r="D7">
+        <v>2.1675E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.7229999999999999E-3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>20.012022000000002</v>
+      </c>
+      <c r="H7">
+        <v>20.010299</v>
+      </c>
+      <c r="I7" s="20">
+        <v>5.7282070000000003</v>
+      </c>
+      <c r="J7">
+        <v>2.169492</v>
+      </c>
+      <c r="K7">
+        <v>244055.98002300001</v>
+      </c>
+      <c r="L7" s="20">
+        <v>5.2996369999999997</v>
+      </c>
+      <c r="M7">
+        <v>8.6628380000000007</v>
+      </c>
+      <c r="N7">
+        <f>$C7/(SUM($C$2:$C$17))*100</f>
+        <v>28.414608120364939</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8">
+        <v>948</v>
+      </c>
+      <c r="D8">
+        <v>4.8200000000000001E-4</v>
+      </c>
+      <c r="E8">
+        <v>3.1524000000000003E-2</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>16.417473000000001</v>
+      </c>
+      <c r="H8">
+        <v>16.385949</v>
+      </c>
+      <c r="I8" s="20">
+        <v>6.5638820000000004</v>
+      </c>
+      <c r="J8">
+        <v>2.9629720000000002</v>
+      </c>
+      <c r="K8">
+        <v>6222.5603840000003</v>
+      </c>
+      <c r="L8" s="20">
+        <v>6.517493</v>
+      </c>
+      <c r="M8">
+        <v>10.301933999999999</v>
+      </c>
+      <c r="N8">
+        <f>$C8/(SUM($C$2:$C$17))*100</f>
+        <v>0.63223603478632029</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9">
+        <v>476</v>
+      </c>
+      <c r="D9">
+        <v>2.42E-4</v>
+      </c>
+      <c r="E9">
+        <v>8.6678000000000005E-2</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>13.458537</v>
+      </c>
+      <c r="H9">
+        <v>13.371859000000001</v>
+      </c>
+      <c r="I9" s="20">
+        <v>5.5752439999999996</v>
+      </c>
+      <c r="J9">
+        <v>2.1362930000000002</v>
+      </c>
+      <c r="K9">
+        <v>2653.8163009999998</v>
+      </c>
+      <c r="L9" s="20">
+        <v>5.5751350000000004</v>
+      </c>
+      <c r="M9">
+        <v>8.2068309999999993</v>
+      </c>
+      <c r="N9">
+        <f>$C9/(SUM($C$2:$C$17))*100</f>
+        <v>0.31745184869017767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10">
+        <v>1124</v>
+      </c>
+      <c r="D10">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="E10">
+        <v>5.3217E-2</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>14.92033</v>
+      </c>
+      <c r="H10">
+        <v>14.867113</v>
+      </c>
+      <c r="I10" s="20">
+        <v>5.2886259999999998</v>
+      </c>
+      <c r="J10">
+        <v>2.3189479999999998</v>
+      </c>
+      <c r="K10">
+        <v>5944.415825</v>
+      </c>
+      <c r="L10" s="20">
+        <v>5.1566210000000003</v>
+      </c>
+      <c r="M10">
+        <v>8.3598140000000001</v>
+      </c>
+      <c r="N10">
+        <f>$C10/(SUM($C$2:$C$17))*100</f>
+        <v>0.74961318892386497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11">
+        <v>869</v>
+      </c>
+      <c r="D11">
+        <v>4.4200000000000001E-4</v>
+      </c>
+      <c r="E11">
+        <v>0.20799599999999999</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>16.395422</v>
+      </c>
+      <c r="H11">
+        <v>16.187425999999999</v>
+      </c>
+      <c r="I11" s="20">
+        <v>6.3673739999999999</v>
+      </c>
+      <c r="J11">
+        <v>2.7761429999999998</v>
+      </c>
+      <c r="K11">
+        <v>5533.2478140000003</v>
+      </c>
+      <c r="L11" s="20">
+        <v>6.1704720000000002</v>
+      </c>
+      <c r="M11">
+        <v>10.14289</v>
+      </c>
+      <c r="N11">
+        <f>$C11/(SUM($C$2:$C$17))*100</f>
+        <v>0.57954969855412686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="E12">
+        <v>4.0183150000000003</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>5.4224649999999999</v>
+      </c>
+      <c r="H12">
+        <v>1.40415</v>
+      </c>
+      <c r="I12" s="20">
+        <v>4.7024749999999997</v>
+      </c>
+      <c r="J12">
+        <v>0.611344</v>
+      </c>
+      <c r="K12">
+        <v>47.024746</v>
+      </c>
+      <c r="L12" s="20">
+        <v>4.6960860000000002</v>
+      </c>
+      <c r="M12">
+        <v>5.4224649999999999</v>
+      </c>
+      <c r="N12">
+        <f>$C12/(SUM($C$2:$C$17))*100</f>
+        <v>6.6691564850877658E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13">
+        <v>138</v>
+      </c>
+      <c r="D13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="E13">
+        <v>1.0212939999999999</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>16.590456</v>
+      </c>
+      <c r="H13">
+        <v>15.569162</v>
+      </c>
+      <c r="I13" s="20">
+        <v>7.0143700000000004</v>
+      </c>
+      <c r="J13">
+        <v>2.7031100000000001</v>
+      </c>
+      <c r="K13">
+        <v>967.98312399999998</v>
+      </c>
+      <c r="L13" s="20">
+        <v>6.8989310000000001</v>
+      </c>
+      <c r="M13">
+        <v>10.739725</v>
+      </c>
+      <c r="N13">
+        <f>$C13/(SUM($C$2:$C$17))*100</f>
+        <v>9.2034359494211182E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14">
+        <v>604</v>
+      </c>
+      <c r="D14">
+        <v>3.0699999999999998E-4</v>
+      </c>
+      <c r="E14">
+        <v>0.45715</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>14.864686000000001</v>
+      </c>
+      <c r="H14">
+        <v>14.407536</v>
+      </c>
+      <c r="I14" s="20">
+        <v>5.1104849999999997</v>
+      </c>
+      <c r="J14">
+        <v>2.2063290000000002</v>
+      </c>
+      <c r="K14">
+        <v>3086.7327919999998</v>
+      </c>
+      <c r="L14" s="20">
+        <v>4.6180560000000002</v>
+      </c>
+      <c r="M14">
+        <v>7.9072839999999998</v>
+      </c>
+      <c r="N14">
+        <f>$C14/(SUM($C$2:$C$17))*100</f>
+        <v>0.4028170516993011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15">
+        <v>3169</v>
+      </c>
+      <c r="D15">
+        <v>1.6119999999999999E-3</v>
+      </c>
+      <c r="E15">
+        <v>0.17449799999999999</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>16.210159000000001</v>
+      </c>
+      <c r="H15">
+        <v>16.035661999999999</v>
+      </c>
+      <c r="I15" s="20">
+        <v>4.8429570000000002</v>
+      </c>
+      <c r="J15">
+        <v>2.0704660000000001</v>
+      </c>
+      <c r="K15">
+        <v>15347.331188</v>
+      </c>
+      <c r="L15" s="20">
+        <v>4.4032419999999997</v>
+      </c>
+      <c r="M15">
+        <v>7.7212899999999998</v>
+      </c>
+      <c r="N15">
+        <f>$C15/(SUM($C$2:$C$17))*100</f>
+        <v>2.1134556901243129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>2680</v>
+      </c>
+      <c r="D16">
+        <v>1.3630000000000001E-3</v>
+      </c>
+      <c r="E16">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>19.829529000000001</v>
+      </c>
+      <c r="H16">
+        <v>19.808729</v>
+      </c>
+      <c r="I16" s="20">
+        <v>5.0365359999999999</v>
+      </c>
+      <c r="J16">
+        <v>2.6395949999999999</v>
+      </c>
+      <c r="K16">
+        <v>13497.915236999999</v>
+      </c>
+      <c r="L16" s="20">
+        <v>4.3763509999999997</v>
+      </c>
+      <c r="M16">
+        <v>8.3830989999999996</v>
+      </c>
+      <c r="N16">
+        <f>$C16/(SUM($C$2:$C$17))*100</f>
+        <v>1.7873339380035214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17">
+        <v>10927</v>
+      </c>
+      <c r="D17">
+        <v>5.5589999999999997E-3</v>
+      </c>
+      <c r="E17">
+        <v>1.7229999999999999E-3</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>17.737905999999999</v>
+      </c>
+      <c r="H17">
+        <v>17.736181999999999</v>
+      </c>
+      <c r="I17" s="20">
+        <v>4.9605990000000002</v>
+      </c>
+      <c r="J17">
+        <v>2.2548059999999999</v>
+      </c>
+      <c r="K17">
+        <v>54204.470384</v>
+      </c>
+      <c r="L17" s="20">
+        <v>4.7589779999999999</v>
+      </c>
+      <c r="M17">
+        <v>7.8119269999999998</v>
+      </c>
+      <c r="N17">
+        <f>$C17/(SUM($C$2:$C$17))*100</f>
+        <v>7.2873872912554027</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+    <sortCondition ref="A1:A17"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main_processing/summary_results/results_stats.xlsx
+++ b/main_processing/summary_results/results_stats.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Documents\GitHub\EIC_manuscript\main_processing\summary_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BA33B2-5513-4D6B-8F2F-3F3C04612B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C6E23-9027-4A0D-82BB-F4FDD40B11E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1392" yWindow="4104" windowWidth="17280" windowHeight="9960" tabRatio="673" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReSALT_values" sheetId="1" r:id="rId1"/>
-    <sheet name="Validation" sheetId="2" r:id="rId2"/>
-    <sheet name="Spat_avg" sheetId="3" r:id="rId3"/>
-    <sheet name="TimeSeries" sheetId="4" r:id="rId4"/>
-    <sheet name="TL_Age" sheetId="5" r:id="rId5"/>
-    <sheet name="TL_Age_EIC" sheetId="10" r:id="rId6"/>
-    <sheet name="Mean r2" sheetId="6" r:id="rId7"/>
-    <sheet name="ADDT" sheetId="7" r:id="rId8"/>
-    <sheet name="geomorphE19" sheetId="9" r:id="rId9"/>
-    <sheet name="geomorphEIC19" sheetId="11" r:id="rId10"/>
+    <sheet name="ReSALT_uncertainty" sheetId="12" r:id="rId2"/>
+    <sheet name="Validation" sheetId="2" r:id="rId3"/>
+    <sheet name="Spat_avg" sheetId="3" r:id="rId4"/>
+    <sheet name="TimeSeries" sheetId="4" r:id="rId5"/>
+    <sheet name="TL_Age" sheetId="5" r:id="rId6"/>
+    <sheet name="TL_Age_EIC" sheetId="10" r:id="rId7"/>
+    <sheet name="Mean r2" sheetId="6" r:id="rId8"/>
+    <sheet name="ADDT" sheetId="7" r:id="rId9"/>
+    <sheet name="geomorphE19" sheetId="9" r:id="rId10"/>
+    <sheet name="geomorphEIC19" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="188">
   <si>
     <t>Year</t>
   </si>
@@ -504,6 +505,111 @@
   </si>
   <si>
     <t>Med_EIC_Uncert_2021</t>
+  </si>
+  <si>
+    <t>0.4 - 1.9</t>
+  </si>
+  <si>
+    <t>0.7 - 1.2</t>
+  </si>
+  <si>
+    <t>4.6  - 47.7</t>
+  </si>
+  <si>
+    <t>10.2 - 26.9</t>
+  </si>
+  <si>
+    <t>1.7 - 7.7</t>
+  </si>
+  <si>
+    <t>1.8 - 5.7</t>
+  </si>
+  <si>
+    <t>2.5 - 4</t>
+  </si>
+  <si>
+    <t>37.5 -145.2</t>
+  </si>
+  <si>
+    <t>61.2 - 102.3</t>
+  </si>
+  <si>
+    <t>4.9 -21.1</t>
+  </si>
+  <si>
+    <t>6.8 -12.6</t>
+  </si>
+  <si>
+    <t>0.7 - 2.4</t>
+  </si>
+  <si>
+    <t>1 - 1.6</t>
+  </si>
+  <si>
+    <t>10.1 - 61.5</t>
+  </si>
+  <si>
+    <t>19.2 - 39</t>
+  </si>
+  <si>
+    <t>2 - 9.5</t>
+  </si>
+  <si>
+    <t>2.7 - 5.5</t>
+  </si>
+  <si>
+    <t>0.4 - 2.1</t>
+  </si>
+  <si>
+    <t>0.6 - 1.2</t>
+  </si>
+  <si>
+    <t>5.4 - 53.9</t>
+  </si>
+  <si>
+    <t>7.8 - 24.3</t>
+  </si>
+  <si>
+    <t>1.8 - 9.2</t>
+  </si>
+  <si>
+    <t>2.4 - 4.8</t>
+  </si>
+  <si>
+    <t>0.5 - 3.7</t>
+  </si>
+  <si>
+    <t>1 - 2.3</t>
+  </si>
+  <si>
+    <t>6.6 - 95.8</t>
+  </si>
+  <si>
+    <t>19.3 - 58.3</t>
+  </si>
+  <si>
+    <t>2 - 14.1</t>
+  </si>
+  <si>
+    <t>3.4 - 7.6</t>
+  </si>
+  <si>
+    <t>1.5 - 4.5</t>
+  </si>
+  <si>
+    <t>2.2 - 3.3</t>
+  </si>
+  <si>
+    <t>33.9 - 114.6</t>
+  </si>
+  <si>
+    <t>55.7 - 83.4</t>
+  </si>
+  <si>
+    <t>4.2 - 17.5</t>
+  </si>
+  <si>
+    <t>5.9 - 10.6</t>
   </si>
 </sst>
 </file>
@@ -702,7 +808,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7784,6 +7890,788 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D42146-3B3D-4C27-9426-7D7671AFC753}">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2">
+        <v>4607</v>
+      </c>
+      <c r="D2">
+        <v>2.3440000000000002E-3</v>
+      </c>
+      <c r="E2">
+        <v>4.5830999999999997E-2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>16.660489999999999</v>
+      </c>
+      <c r="H2">
+        <v>16.614659</v>
+      </c>
+      <c r="I2" s="20">
+        <v>5.290305</v>
+      </c>
+      <c r="J2">
+        <v>2.3120959999999999</v>
+      </c>
+      <c r="K2">
+        <v>24372.434228999999</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4.6848109999999998</v>
+      </c>
+      <c r="M2">
+        <v>8.5788930000000008</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N17" si="0">$C2/(SUM($C$2:$C$17))*100</f>
+        <v>3.0724803926799336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>38397</v>
+      </c>
+      <c r="D3">
+        <v>1.9533999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>6.2798999999999994E-2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>19.544087999999999</v>
+      </c>
+      <c r="H3">
+        <v>19.481289</v>
+      </c>
+      <c r="I3" s="20">
+        <v>5.7574149999999999</v>
+      </c>
+      <c r="J3">
+        <v>2.398174</v>
+      </c>
+      <c r="K3">
+        <v>221067.47383599999</v>
+      </c>
+      <c r="L3" s="20">
+        <v>5.1605259999999999</v>
+      </c>
+      <c r="M3">
+        <v>9.1302830000000004</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>25.607560155791496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4">
+        <v>19077</v>
+      </c>
+      <c r="D4">
+        <v>9.7050000000000001E-3</v>
+      </c>
+      <c r="E4">
+        <v>6.8499999999999995E-4</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>22.62067</v>
+      </c>
+      <c r="H4">
+        <v>22.619985</v>
+      </c>
+      <c r="I4" s="20">
+        <v>6.1604219999999996</v>
+      </c>
+      <c r="J4">
+        <v>2.885014</v>
+      </c>
+      <c r="K4">
+        <v>117522.365229</v>
+      </c>
+      <c r="L4" s="20">
+        <v>5.5759090000000002</v>
+      </c>
+      <c r="M4">
+        <v>10.313598000000001</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>12.72274982660193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5">
+        <v>16321</v>
+      </c>
+      <c r="D5">
+        <v>8.3029999999999996E-3</v>
+      </c>
+      <c r="E5">
+        <v>4.5310000000000003E-2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>17.568557999999999</v>
+      </c>
+      <c r="H5">
+        <v>17.523247000000001</v>
+      </c>
+      <c r="I5" s="20">
+        <v>6.3288960000000003</v>
+      </c>
+      <c r="J5">
+        <v>2.171116</v>
+      </c>
+      <c r="K5">
+        <v>103293.90561099999</v>
+      </c>
+      <c r="L5" s="20">
+        <v>5.9660849999999996</v>
+      </c>
+      <c r="M5">
+        <v>9.3300599999999996</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>10.884730299311743</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>7991</v>
+      </c>
+      <c r="D6">
+        <v>4.065E-3</v>
+      </c>
+      <c r="E6">
+        <v>0.25051800000000002</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>18.078802</v>
+      </c>
+      <c r="H6">
+        <v>17.828284</v>
+      </c>
+      <c r="I6" s="20">
+        <v>5.4433720000000001</v>
+      </c>
+      <c r="J6">
+        <v>2.045506</v>
+      </c>
+      <c r="K6">
+        <v>43497.985368000001</v>
+      </c>
+      <c r="L6" s="20">
+        <v>4.9719379999999997</v>
+      </c>
+      <c r="M6">
+        <v>8.1958540000000006</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>5.3293229472336341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7">
+        <v>42606</v>
+      </c>
+      <c r="D7">
+        <v>2.1675E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.7229999999999999E-3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>20.012022000000002</v>
+      </c>
+      <c r="H7">
+        <v>20.010299</v>
+      </c>
+      <c r="I7" s="20">
+        <v>5.7282070000000003</v>
+      </c>
+      <c r="J7">
+        <v>2.169492</v>
+      </c>
+      <c r="K7">
+        <v>244055.98002300001</v>
+      </c>
+      <c r="L7" s="20">
+        <v>5.2996369999999997</v>
+      </c>
+      <c r="M7">
+        <v>8.6628380000000007</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>28.414608120364939</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8">
+        <v>948</v>
+      </c>
+      <c r="D8">
+        <v>4.8200000000000001E-4</v>
+      </c>
+      <c r="E8">
+        <v>3.1524000000000003E-2</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>16.417473000000001</v>
+      </c>
+      <c r="H8">
+        <v>16.385949</v>
+      </c>
+      <c r="I8" s="20">
+        <v>6.5638820000000004</v>
+      </c>
+      <c r="J8">
+        <v>2.9629720000000002</v>
+      </c>
+      <c r="K8">
+        <v>6222.5603840000003</v>
+      </c>
+      <c r="L8" s="20">
+        <v>6.517493</v>
+      </c>
+      <c r="M8">
+        <v>10.301933999999999</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0.63223603478632029</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9">
+        <v>476</v>
+      </c>
+      <c r="D9">
+        <v>2.42E-4</v>
+      </c>
+      <c r="E9">
+        <v>8.6678000000000005E-2</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>13.458537</v>
+      </c>
+      <c r="H9">
+        <v>13.371859000000001</v>
+      </c>
+      <c r="I9" s="20">
+        <v>5.5752439999999996</v>
+      </c>
+      <c r="J9">
+        <v>2.1362930000000002</v>
+      </c>
+      <c r="K9">
+        <v>2653.8163009999998</v>
+      </c>
+      <c r="L9" s="20">
+        <v>5.5751350000000004</v>
+      </c>
+      <c r="M9">
+        <v>8.2068309999999993</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>0.31745184869017767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10">
+        <v>1124</v>
+      </c>
+      <c r="D10">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="E10">
+        <v>5.3217E-2</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>14.92033</v>
+      </c>
+      <c r="H10">
+        <v>14.867113</v>
+      </c>
+      <c r="I10" s="20">
+        <v>5.2886259999999998</v>
+      </c>
+      <c r="J10">
+        <v>2.3189479999999998</v>
+      </c>
+      <c r="K10">
+        <v>5944.415825</v>
+      </c>
+      <c r="L10" s="20">
+        <v>5.1566210000000003</v>
+      </c>
+      <c r="M10">
+        <v>8.3598140000000001</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0.74961318892386497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11">
+        <v>869</v>
+      </c>
+      <c r="D11">
+        <v>4.4200000000000001E-4</v>
+      </c>
+      <c r="E11">
+        <v>0.20799599999999999</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>16.395422</v>
+      </c>
+      <c r="H11">
+        <v>16.187425999999999</v>
+      </c>
+      <c r="I11" s="20">
+        <v>6.3673739999999999</v>
+      </c>
+      <c r="J11">
+        <v>2.7761429999999998</v>
+      </c>
+      <c r="K11">
+        <v>5533.2478140000003</v>
+      </c>
+      <c r="L11" s="20">
+        <v>6.1704720000000002</v>
+      </c>
+      <c r="M11">
+        <v>10.14289</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>0.57954969855412686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="E12">
+        <v>4.0183150000000003</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>5.4224649999999999</v>
+      </c>
+      <c r="H12">
+        <v>1.40415</v>
+      </c>
+      <c r="I12" s="20">
+        <v>4.7024749999999997</v>
+      </c>
+      <c r="J12">
+        <v>0.611344</v>
+      </c>
+      <c r="K12">
+        <v>47.024746</v>
+      </c>
+      <c r="L12" s="20">
+        <v>4.6960860000000002</v>
+      </c>
+      <c r="M12">
+        <v>5.4224649999999999</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="0"/>
+        <v>6.6691564850877658E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13">
+        <v>138</v>
+      </c>
+      <c r="D13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="E13">
+        <v>1.0212939999999999</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>16.590456</v>
+      </c>
+      <c r="H13">
+        <v>15.569162</v>
+      </c>
+      <c r="I13" s="20">
+        <v>7.0143700000000004</v>
+      </c>
+      <c r="J13">
+        <v>2.7031100000000001</v>
+      </c>
+      <c r="K13">
+        <v>967.98312399999998</v>
+      </c>
+      <c r="L13" s="20">
+        <v>6.8989310000000001</v>
+      </c>
+      <c r="M13">
+        <v>10.739725</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="0"/>
+        <v>9.2034359494211182E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14">
+        <v>604</v>
+      </c>
+      <c r="D14">
+        <v>3.0699999999999998E-4</v>
+      </c>
+      <c r="E14">
+        <v>0.45715</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>14.864686000000001</v>
+      </c>
+      <c r="H14">
+        <v>14.407536</v>
+      </c>
+      <c r="I14" s="20">
+        <v>5.1104849999999997</v>
+      </c>
+      <c r="J14">
+        <v>2.2063290000000002</v>
+      </c>
+      <c r="K14">
+        <v>3086.7327919999998</v>
+      </c>
+      <c r="L14" s="20">
+        <v>4.6180560000000002</v>
+      </c>
+      <c r="M14">
+        <v>7.9072839999999998</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.4028170516993011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15">
+        <v>3169</v>
+      </c>
+      <c r="D15">
+        <v>1.6119999999999999E-3</v>
+      </c>
+      <c r="E15">
+        <v>0.17449799999999999</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>16.210159000000001</v>
+      </c>
+      <c r="H15">
+        <v>16.035661999999999</v>
+      </c>
+      <c r="I15" s="20">
+        <v>4.8429570000000002</v>
+      </c>
+      <c r="J15">
+        <v>2.0704660000000001</v>
+      </c>
+      <c r="K15">
+        <v>15347.331188</v>
+      </c>
+      <c r="L15" s="20">
+        <v>4.4032419999999997</v>
+      </c>
+      <c r="M15">
+        <v>7.7212899999999998</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="0"/>
+        <v>2.1134556901243129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>2680</v>
+      </c>
+      <c r="D16">
+        <v>1.3630000000000001E-3</v>
+      </c>
+      <c r="E16">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>19.829529000000001</v>
+      </c>
+      <c r="H16">
+        <v>19.808729</v>
+      </c>
+      <c r="I16" s="20">
+        <v>5.0365359999999999</v>
+      </c>
+      <c r="J16">
+        <v>2.6395949999999999</v>
+      </c>
+      <c r="K16">
+        <v>13497.915236999999</v>
+      </c>
+      <c r="L16" s="20">
+        <v>4.3763509999999997</v>
+      </c>
+      <c r="M16">
+        <v>8.3830989999999996</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="0"/>
+        <v>1.7873339380035214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17">
+        <v>10927</v>
+      </c>
+      <c r="D17">
+        <v>5.5589999999999997E-3</v>
+      </c>
+      <c r="E17">
+        <v>1.7229999999999999E-3</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>17.737905999999999</v>
+      </c>
+      <c r="H17">
+        <v>17.736181999999999</v>
+      </c>
+      <c r="I17" s="20">
+        <v>4.9605990000000002</v>
+      </c>
+      <c r="J17">
+        <v>2.2548059999999999</v>
+      </c>
+      <c r="K17">
+        <v>54204.470384</v>
+      </c>
+      <c r="L17" s="20">
+        <v>4.7589779999999999</v>
+      </c>
+      <c r="M17">
+        <v>7.8119269999999998</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="0"/>
+        <v>7.2873872912554027</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+    <sortCondition ref="A1:A17"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF7E68A-EDBB-4BD3-AF33-8C03844816FE}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7871,7 +8759,7 @@
         <v>75.669032000000001</v>
       </c>
       <c r="M2">
-        <f>$C2/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" ref="M2:M17" si="0">$C2/(SUM($C$2:$C$17))*100</f>
         <v>0.54971754844196075</v>
       </c>
     </row>
@@ -7913,7 +8801,7 @@
         <v>35.801223</v>
       </c>
       <c r="M3">
-        <f>$C3/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>0.10478041669197595</v>
       </c>
     </row>
@@ -7955,7 +8843,7 @@
         <v>41.026603000000001</v>
       </c>
       <c r="M4">
-        <f>$C4/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>0.73953714389843894</v>
       </c>
     </row>
@@ -7997,7 +8885,7 @@
         <v>26.036200999999998</v>
       </c>
       <c r="M5">
-        <f>$C5/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>7.5927838182591268E-3</v>
       </c>
     </row>
@@ -8039,7 +8927,7 @@
         <v>34.941875000000003</v>
       </c>
       <c r="M6">
-        <f>$C6/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>0.60818198384255606</v>
       </c>
     </row>
@@ -8081,7 +8969,7 @@
         <v>33.462648999999999</v>
       </c>
       <c r="M7">
-        <f>$C7/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>13.019346413168925</v>
       </c>
     </row>
@@ -8123,7 +9011,7 @@
         <v>48.830938000000003</v>
       </c>
       <c r="M8">
-        <f>$C8/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>0.31130413654862421</v>
       </c>
     </row>
@@ -8165,7 +9053,7 @@
         <v>25.210070999999999</v>
       </c>
       <c r="M9">
-        <f>$C9/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>3.6088501488185627</v>
       </c>
     </row>
@@ -8207,7 +9095,7 @@
         <v>27.927783999999999</v>
       </c>
       <c r="M10">
-        <f>$C10/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>27.178369677458541</v>
       </c>
     </row>
@@ -8249,7 +9137,7 @@
         <v>30.818484999999999</v>
       </c>
       <c r="M11">
-        <f>$C11/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>1.7554516187815099</v>
       </c>
     </row>
@@ -8291,7 +9179,7 @@
         <v>27.432120999999999</v>
       </c>
       <c r="M12">
-        <f>$C12/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>3.267174876996902</v>
       </c>
     </row>
@@ -8333,7 +9221,7 @@
         <v>26.266939000000001</v>
       </c>
       <c r="M13">
-        <f>$C13/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>0.42595517220433698</v>
       </c>
     </row>
@@ -8375,7 +9263,7 @@
         <v>24.258673000000002</v>
       </c>
       <c r="M14">
-        <f>$C14/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>2.2300006074227054</v>
       </c>
     </row>
@@ -8417,7 +9305,7 @@
         <v>23.926466000000001</v>
       </c>
       <c r="M15">
-        <f>$C15/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>5.475915689728482</v>
       </c>
     </row>
@@ -8459,7 +9347,7 @@
         <v>19.928699000000002</v>
       </c>
       <c r="M16">
-        <f>$C16/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>11.540272125372047</v>
       </c>
     </row>
@@ -8501,7 +9389,7 @@
         <v>18.99119</v>
       </c>
       <c r="M17">
-        <f>$C17/(SUM($C$2:$C$17))*100</f>
+        <f t="shared" si="0"/>
         <v>29.177549656806175</v>
       </c>
     </row>
@@ -8514,6 +9402,273 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{979363C7-3375-4C48-A3C1-4372A047B7FE}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2018</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="6">
+        <v>17.5</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2019</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="6">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="6">
+        <v>9</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="25">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="6">
+        <v>28</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="6">
+        <v>37.1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="7">
+        <v>68.2</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F5F117-B6A8-4FFE-91EB-60A6448A24F9}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8734,7 +9889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A5BBD5-0723-41D4-90F3-7A96661EB37D}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8981,7 +10136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94EC12B8-9383-4714-BC97-ED13236D7219}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9112,7 +10267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9F15C4-2ABE-401A-A7E7-6DA16866D145}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9569,7 +10724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB75B4DC-2B7A-44C2-93AB-1567121CF63C}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9608,10 +10763,10 @@
       <c r="I1" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="3" t="s">
         <v>150</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -10017,7 +11172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{377D1681-D2CD-4561-BD67-58B5F6A4E1BF}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10133,7 +11288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA21557-DC7E-4A6F-8F8A-F10950C41832}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10264,786 +11419,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D42146-3B3D-4C27-9426-7D7671AFC753}">
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J1" t="s">
-        <v>141</v>
-      </c>
-      <c r="K1" t="s">
-        <v>142</v>
-      </c>
-      <c r="L1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2">
-        <v>4607</v>
-      </c>
-      <c r="D2">
-        <v>2.3440000000000002E-3</v>
-      </c>
-      <c r="E2">
-        <v>4.5830999999999997E-2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>16.660489999999999</v>
-      </c>
-      <c r="H2">
-        <v>16.614659</v>
-      </c>
-      <c r="I2" s="20">
-        <v>5.290305</v>
-      </c>
-      <c r="J2">
-        <v>2.3120959999999999</v>
-      </c>
-      <c r="K2">
-        <v>24372.434228999999</v>
-      </c>
-      <c r="L2" s="20">
-        <v>4.6848109999999998</v>
-      </c>
-      <c r="M2">
-        <v>8.5788930000000008</v>
-      </c>
-      <c r="N2">
-        <f>$C2/(SUM($C$2:$C$17))*100</f>
-        <v>3.0724803926799336</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3">
-        <v>38397</v>
-      </c>
-      <c r="D3">
-        <v>1.9533999999999999E-2</v>
-      </c>
-      <c r="E3">
-        <v>6.2798999999999994E-2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>19.544087999999999</v>
-      </c>
-      <c r="H3">
-        <v>19.481289</v>
-      </c>
-      <c r="I3" s="20">
-        <v>5.7574149999999999</v>
-      </c>
-      <c r="J3">
-        <v>2.398174</v>
-      </c>
-      <c r="K3">
-        <v>221067.47383599999</v>
-      </c>
-      <c r="L3" s="20">
-        <v>5.1605259999999999</v>
-      </c>
-      <c r="M3">
-        <v>9.1302830000000004</v>
-      </c>
-      <c r="N3">
-        <f>$C3/(SUM($C$2:$C$17))*100</f>
-        <v>25.607560155791496</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4">
-        <v>19077</v>
-      </c>
-      <c r="D4">
-        <v>9.7050000000000001E-3</v>
-      </c>
-      <c r="E4">
-        <v>6.8499999999999995E-4</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>22.62067</v>
-      </c>
-      <c r="H4">
-        <v>22.619985</v>
-      </c>
-      <c r="I4" s="20">
-        <v>6.1604219999999996</v>
-      </c>
-      <c r="J4">
-        <v>2.885014</v>
-      </c>
-      <c r="K4">
-        <v>117522.365229</v>
-      </c>
-      <c r="L4" s="20">
-        <v>5.5759090000000002</v>
-      </c>
-      <c r="M4">
-        <v>10.313598000000001</v>
-      </c>
-      <c r="N4">
-        <f>$C4/(SUM($C$2:$C$17))*100</f>
-        <v>12.72274982660193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5">
-        <v>16321</v>
-      </c>
-      <c r="D5">
-        <v>8.3029999999999996E-3</v>
-      </c>
-      <c r="E5">
-        <v>4.5310000000000003E-2</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>17.568557999999999</v>
-      </c>
-      <c r="H5">
-        <v>17.523247000000001</v>
-      </c>
-      <c r="I5" s="20">
-        <v>6.3288960000000003</v>
-      </c>
-      <c r="J5">
-        <v>2.171116</v>
-      </c>
-      <c r="K5">
-        <v>103293.90561099999</v>
-      </c>
-      <c r="L5" s="20">
-        <v>5.9660849999999996</v>
-      </c>
-      <c r="M5">
-        <v>9.3300599999999996</v>
-      </c>
-      <c r="N5">
-        <f>$C5/(SUM($C$2:$C$17))*100</f>
-        <v>10.884730299311743</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6">
-        <v>7991</v>
-      </c>
-      <c r="D6">
-        <v>4.065E-3</v>
-      </c>
-      <c r="E6">
-        <v>0.25051800000000002</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>18.078802</v>
-      </c>
-      <c r="H6">
-        <v>17.828284</v>
-      </c>
-      <c r="I6" s="20">
-        <v>5.4433720000000001</v>
-      </c>
-      <c r="J6">
-        <v>2.045506</v>
-      </c>
-      <c r="K6">
-        <v>43497.985368000001</v>
-      </c>
-      <c r="L6" s="20">
-        <v>4.9719379999999997</v>
-      </c>
-      <c r="M6">
-        <v>8.1958540000000006</v>
-      </c>
-      <c r="N6">
-        <f>$C6/(SUM($C$2:$C$17))*100</f>
-        <v>5.3293229472336341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7">
-        <v>42606</v>
-      </c>
-      <c r="D7">
-        <v>2.1675E-2</v>
-      </c>
-      <c r="E7">
-        <v>1.7229999999999999E-3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>20.012022000000002</v>
-      </c>
-      <c r="H7">
-        <v>20.010299</v>
-      </c>
-      <c r="I7" s="20">
-        <v>5.7282070000000003</v>
-      </c>
-      <c r="J7">
-        <v>2.169492</v>
-      </c>
-      <c r="K7">
-        <v>244055.98002300001</v>
-      </c>
-      <c r="L7" s="20">
-        <v>5.2996369999999997</v>
-      </c>
-      <c r="M7">
-        <v>8.6628380000000007</v>
-      </c>
-      <c r="N7">
-        <f>$C7/(SUM($C$2:$C$17))*100</f>
-        <v>28.414608120364939</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8">
-        <v>948</v>
-      </c>
-      <c r="D8">
-        <v>4.8200000000000001E-4</v>
-      </c>
-      <c r="E8">
-        <v>3.1524000000000003E-2</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <v>16.417473000000001</v>
-      </c>
-      <c r="H8">
-        <v>16.385949</v>
-      </c>
-      <c r="I8" s="20">
-        <v>6.5638820000000004</v>
-      </c>
-      <c r="J8">
-        <v>2.9629720000000002</v>
-      </c>
-      <c r="K8">
-        <v>6222.5603840000003</v>
-      </c>
-      <c r="L8" s="20">
-        <v>6.517493</v>
-      </c>
-      <c r="M8">
-        <v>10.301933999999999</v>
-      </c>
-      <c r="N8">
-        <f>$C8/(SUM($C$2:$C$17))*100</f>
-        <v>0.63223603478632029</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9">
-        <v>476</v>
-      </c>
-      <c r="D9">
-        <v>2.42E-4</v>
-      </c>
-      <c r="E9">
-        <v>8.6678000000000005E-2</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9">
-        <v>13.458537</v>
-      </c>
-      <c r="H9">
-        <v>13.371859000000001</v>
-      </c>
-      <c r="I9" s="20">
-        <v>5.5752439999999996</v>
-      </c>
-      <c r="J9">
-        <v>2.1362930000000002</v>
-      </c>
-      <c r="K9">
-        <v>2653.8163009999998</v>
-      </c>
-      <c r="L9" s="20">
-        <v>5.5751350000000004</v>
-      </c>
-      <c r="M9">
-        <v>8.2068309999999993</v>
-      </c>
-      <c r="N9">
-        <f>$C9/(SUM($C$2:$C$17))*100</f>
-        <v>0.31745184869017767</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10">
-        <v>1124</v>
-      </c>
-      <c r="D10">
-        <v>5.7200000000000003E-4</v>
-      </c>
-      <c r="E10">
-        <v>5.3217E-2</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>14.92033</v>
-      </c>
-      <c r="H10">
-        <v>14.867113</v>
-      </c>
-      <c r="I10" s="20">
-        <v>5.2886259999999998</v>
-      </c>
-      <c r="J10">
-        <v>2.3189479999999998</v>
-      </c>
-      <c r="K10">
-        <v>5944.415825</v>
-      </c>
-      <c r="L10" s="20">
-        <v>5.1566210000000003</v>
-      </c>
-      <c r="M10">
-        <v>8.3598140000000001</v>
-      </c>
-      <c r="N10">
-        <f>$C10/(SUM($C$2:$C$17))*100</f>
-        <v>0.74961318892386497</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11">
-        <v>869</v>
-      </c>
-      <c r="D11">
-        <v>4.4200000000000001E-4</v>
-      </c>
-      <c r="E11">
-        <v>0.20799599999999999</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>16.395422</v>
-      </c>
-      <c r="H11">
-        <v>16.187425999999999</v>
-      </c>
-      <c r="I11" s="20">
-        <v>6.3673739999999999</v>
-      </c>
-      <c r="J11">
-        <v>2.7761429999999998</v>
-      </c>
-      <c r="K11">
-        <v>5533.2478140000003</v>
-      </c>
-      <c r="L11" s="20">
-        <v>6.1704720000000002</v>
-      </c>
-      <c r="M11">
-        <v>10.14289</v>
-      </c>
-      <c r="N11">
-        <f>$C11/(SUM($C$2:$C$17))*100</f>
-        <v>0.57954969855412686</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="E12">
-        <v>4.0183150000000003</v>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>5.4224649999999999</v>
-      </c>
-      <c r="H12">
-        <v>1.40415</v>
-      </c>
-      <c r="I12" s="20">
-        <v>4.7024749999999997</v>
-      </c>
-      <c r="J12">
-        <v>0.611344</v>
-      </c>
-      <c r="K12">
-        <v>47.024746</v>
-      </c>
-      <c r="L12" s="20">
-        <v>4.6960860000000002</v>
-      </c>
-      <c r="M12">
-        <v>5.4224649999999999</v>
-      </c>
-      <c r="N12">
-        <f>$C12/(SUM($C$2:$C$17))*100</f>
-        <v>6.6691564850877658E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13">
-        <v>138</v>
-      </c>
-      <c r="D13">
-        <v>6.9999999999999994E-5</v>
-      </c>
-      <c r="E13">
-        <v>1.0212939999999999</v>
-      </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>16.590456</v>
-      </c>
-      <c r="H13">
-        <v>15.569162</v>
-      </c>
-      <c r="I13" s="20">
-        <v>7.0143700000000004</v>
-      </c>
-      <c r="J13">
-        <v>2.7031100000000001</v>
-      </c>
-      <c r="K13">
-        <v>967.98312399999998</v>
-      </c>
-      <c r="L13" s="20">
-        <v>6.8989310000000001</v>
-      </c>
-      <c r="M13">
-        <v>10.739725</v>
-      </c>
-      <c r="N13">
-        <f>$C13/(SUM($C$2:$C$17))*100</f>
-        <v>9.2034359494211182E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14">
-        <v>604</v>
-      </c>
-      <c r="D14">
-        <v>3.0699999999999998E-4</v>
-      </c>
-      <c r="E14">
-        <v>0.45715</v>
-      </c>
-      <c r="F14">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>14.864686000000001</v>
-      </c>
-      <c r="H14">
-        <v>14.407536</v>
-      </c>
-      <c r="I14" s="20">
-        <v>5.1104849999999997</v>
-      </c>
-      <c r="J14">
-        <v>2.2063290000000002</v>
-      </c>
-      <c r="K14">
-        <v>3086.7327919999998</v>
-      </c>
-      <c r="L14" s="20">
-        <v>4.6180560000000002</v>
-      </c>
-      <c r="M14">
-        <v>7.9072839999999998</v>
-      </c>
-      <c r="N14">
-        <f>$C14/(SUM($C$2:$C$17))*100</f>
-        <v>0.4028170516993011</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15">
-        <v>3169</v>
-      </c>
-      <c r="D15">
-        <v>1.6119999999999999E-3</v>
-      </c>
-      <c r="E15">
-        <v>0.17449799999999999</v>
-      </c>
-      <c r="F15">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>16.210159000000001</v>
-      </c>
-      <c r="H15">
-        <v>16.035661999999999</v>
-      </c>
-      <c r="I15" s="20">
-        <v>4.8429570000000002</v>
-      </c>
-      <c r="J15">
-        <v>2.0704660000000001</v>
-      </c>
-      <c r="K15">
-        <v>15347.331188</v>
-      </c>
-      <c r="L15" s="20">
-        <v>4.4032419999999997</v>
-      </c>
-      <c r="M15">
-        <v>7.7212899999999998</v>
-      </c>
-      <c r="N15">
-        <f>$C15/(SUM($C$2:$C$17))*100</f>
-        <v>2.1134556901243129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16">
-        <v>2680</v>
-      </c>
-      <c r="D16">
-        <v>1.3630000000000001E-3</v>
-      </c>
-      <c r="E16">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="F16">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>19.829529000000001</v>
-      </c>
-      <c r="H16">
-        <v>19.808729</v>
-      </c>
-      <c r="I16" s="20">
-        <v>5.0365359999999999</v>
-      </c>
-      <c r="J16">
-        <v>2.6395949999999999</v>
-      </c>
-      <c r="K16">
-        <v>13497.915236999999</v>
-      </c>
-      <c r="L16" s="20">
-        <v>4.3763509999999997</v>
-      </c>
-      <c r="M16">
-        <v>8.3830989999999996</v>
-      </c>
-      <c r="N16">
-        <f>$C16/(SUM($C$2:$C$17))*100</f>
-        <v>1.7873339380035214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17">
-        <v>10927</v>
-      </c>
-      <c r="D17">
-        <v>5.5589999999999997E-3</v>
-      </c>
-      <c r="E17">
-        <v>1.7229999999999999E-3</v>
-      </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>17.737905999999999</v>
-      </c>
-      <c r="H17">
-        <v>17.736181999999999</v>
-      </c>
-      <c r="I17" s="20">
-        <v>4.9605990000000002</v>
-      </c>
-      <c r="J17">
-        <v>2.2548059999999999</v>
-      </c>
-      <c r="K17">
-        <v>54204.470384</v>
-      </c>
-      <c r="L17" s="20">
-        <v>4.7589779999999999</v>
-      </c>
-      <c r="M17">
-        <v>7.8119269999999998</v>
-      </c>
-      <c r="N17">
-        <f>$C17/(SUM($C$2:$C$17))*100</f>
-        <v>7.2873872912554027</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
-    <sortCondition ref="A1:A17"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/main_processing/summary_results/results_stats.xlsx
+++ b/main_processing/summary_results/results_stats.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C6E23-9027-4A0D-82BB-F4FDD40B11E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1392" yWindow="4104" windowWidth="17280" windowHeight="9960" tabRatio="673" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="673" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReSALT_values" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -808,7 +808,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9530,7 +9529,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5">
         <v>2020</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -9562,7 +9561,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6">
         <v>2021</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -9594,7 +9593,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7">
         <v>2022</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -9626,7 +9625,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8">
         <v>2023</v>
       </c>
       <c r="B8" s="6" t="s">
